--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128786733</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56883</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Frängsmyrbäcken NV Övre Buddbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>800100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7324673</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128786733</v>
       </c>
       <c r="B3" t="n">
-        <v>56883</v>
+        <v>56910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128786733</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128786733</v>
       </c>
       <c r="B3" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128786733</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>56918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128786733</v>
       </c>
       <c r="B3" t="n">
-        <v>56918</v>
+        <v>56920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>109914906</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -804,27 +799,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128786733</v>
+        <v>107269106</v>
       </c>
       <c r="B3" t="n">
-        <v>56920</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,13 +829,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -885,22 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,27 +922,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134089689</v>
+        <v>128786733</v>
       </c>
       <c r="B4" t="n">
-        <v>57796</v>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,18 +952,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1008,27 +1003,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stora aspar med hål.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,27 +1045,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134089694</v>
+        <v>134089689</v>
       </c>
       <c r="B5" t="n">
-        <v>58308</v>
+        <v>57796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103008</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,14 +1075,18 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1150,6 +1144,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stora aspar med hål.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1171,6 +1170,360 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109914918</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frängsmyrbäcken NV Övre Buddbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>800100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7324673</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134089694</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58308</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frängsmyrbäcken NV Övre Buddbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>800100</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7324673</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109914912</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frängsmyrbäcken NV Övre Buddbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>800100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7324673</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47498-2022 artfynd.xlsx
+++ b/artfynd/A 47498-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109914906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107269106</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128786733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134089689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109914918</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134089694</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1524,8 +1559,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109914912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>